--- a/data/trending_integrated_20261021_12.xlsx
+++ b/data/trending_integrated_20261021_12.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10571232757</v>
+        <v>10572345257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15000</v>
+        <v>14950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.17%</t>
+          <t>'+23.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>88233900680</v>
+        <v>88674869715</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11140</v>
+        <v>11170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.02%</t>
+          <t>'+14.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G4" t="n">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>233489055655</v>
+        <v>236224623010</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주잔고 급증 및 시총 대비 높은 성장성. 연말 1조 돌파 기대.</t>
+          <t>인공지능 데이터센터 수주 잔고 증가 및 신고가 경신. 로봇 섹터 강세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주잔고', 'AI', '신고가']</t>
+          <t>['수주잔고', '신고가', '로봇']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9520</v>
+        <v>9390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+8.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H5" t="n">
         <v>5.34</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>24713797980</v>
+        <v>26018043855</v>
       </c>
       <c r="P5" t="n">
         <v>14940</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>나스닥 상장 철회 관련 불확실성 해소 기대감. 차기 성장 동력 확보 노력.</t>
+          <t>자회사 나스닥 상장 철회 이슈 속 거래량 증가 및 상승 기대감. 영업이익 호조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['나스닥', '상장철회', '테슬라']</t>
+          <t>['나스닥', '영업이익', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225500</v>
+        <v>224000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.62%</t>
+          <t>'+5.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G6" t="n">
-        <v>1832</v>
+        <v>1866</v>
       </c>
       <c r="H6" t="n">
         <v>46.08</v>
@@ -978,7 +978,7 @@
         <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>2051921836000</v>
+        <v>2112579952000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 순매수세 유입 및 반도체 관련 지정학적 이슈 부각. 4분기 실적 개선 기대감.</t>
+          <t>외인 동반 매수세 유입 및 미국발 반도체 관련 뉴스에 따른 상승 기대감. 25만원 돌파 여부가 관건.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인유입', '반도체', '지정학적']</t>
+          <t>['반도체', '외인매수', '실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1296000</v>
+        <v>1292000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.97%</t>
+          <t>'+5.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G7" t="n">
-        <v>1687</v>
+        <v>1755</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>3021563540000</v>
+        <v>3066870962500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 종료 후 마이크론 파업 관련 속보와 함께 금융기관 매도세 관찰. 일부에서는 외인/기관 순매수를 긍정적 신호로 해석하나, 솔리다임 상장 관련 부정적 전망도 공존.</t>
+          <t>자사주 매입 완료 및 마이크론 파업 예고 등의 뉴스 반영. 외인/기관 순매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주 매입', '마이크론', '솔리다임']</t>
+          <t>['자사주', '외인매수', '마이크론']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14760</v>
+        <v>14790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1153,7 +1153,7 @@
         <v>14340</v>
       </c>
       <c r="L8" t="n">
-        <v>14790</v>
+        <v>14820</v>
       </c>
       <c r="M8" t="n">
         <v>14340</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>21313700480</v>
+        <v>22592573380</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관 및 외국인 순매수 유입. 실적 개선 및 목표가 상향 가능성.</t>
+          <t>실적 기반 상승 기대감 있으나, 주가 조작 및 정치적 이슈 언급하며 부정적 논조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관매수', '외국인', '실적주']</t>
+          <t>['실적', '주가조작', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3095</v>
+        <v>2935</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.69%</t>
+          <t>'+3.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.73</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2985</v>
+        <v>2840</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2855</v>
       </c>
       <c r="N9" t="n">
-        <v>0.73</v>
+        <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>9337000000</v>
+        <v>16117797689</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>19950</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1913</v>
       </c>
       <c r="R9" t="n">
-        <v>-32000</v>
+        <v>-1166000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2920</v>
+        <v>7440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
         <v>71</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="H10" t="n">
-        <v>5.82</v>
+        <v>25.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2840</v>
+        <v>7270</v>
       </c>
       <c r="K10" t="n">
-        <v>3100</v>
+        <v>7360</v>
       </c>
       <c r="L10" t="n">
-        <v>3300</v>
+        <v>7520</v>
       </c>
       <c r="M10" t="n">
-        <v>2855</v>
+        <v>7250</v>
       </c>
       <c r="N10" t="n">
-        <v>5.91</v>
+        <v>25.4</v>
       </c>
       <c r="O10" t="n">
-        <v>16029794494</v>
+        <v>9494980700</v>
       </c>
       <c r="P10" t="n">
-        <v>19950</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>1913</v>
+        <v>7190</v>
       </c>
       <c r="R10" t="n">
-        <v>-1166000</v>
+        <v>131000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7440</v>
+        <v>17670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+2.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="H11" t="n">
-        <v>25.45</v>
+        <v>27.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,152 +1423,152 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7270</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>7360</v>
+        <v>17480</v>
       </c>
       <c r="L11" t="n">
-        <v>7520</v>
+        <v>17820</v>
       </c>
       <c r="M11" t="n">
-        <v>7250</v>
+        <v>17170</v>
       </c>
       <c r="N11" t="n">
-        <v>25.4</v>
+        <v>27.78</v>
       </c>
       <c r="O11" t="n">
-        <v>9282771590</v>
+        <v>27643319170</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>7190</v>
+        <v>17170</v>
       </c>
       <c r="R11" t="n">
-        <v>131000</v>
+        <v>146000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>24000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
+          <t>조선, 방산, 원전 섹터 전반의 약세. 실적 부진 및 시장 기대치 하회.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
+          <t>['조선', '방산', '실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17680</v>
+        <v>1604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44</v>
+      </c>
+      <c r="G12" t="n">
+        <v>198</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1573</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1715</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1573</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O12" t="n">
+        <v>27605260594</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2970</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>890</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-746000</v>
+      </c>
+      <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>82</v>
-      </c>
-      <c r="F12" t="n">
-        <v>47</v>
-      </c>
-      <c r="G12" t="n">
-        <v>175</v>
-      </c>
-      <c r="H12" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>17320</v>
-      </c>
-      <c r="K12" t="n">
-        <v>17480</v>
-      </c>
-      <c r="L12" t="n">
-        <v>17820</v>
-      </c>
-      <c r="M12" t="n">
-        <v>17170</v>
-      </c>
-      <c r="N12" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="O12" t="n">
-        <v>27094852445</v>
-      </c>
-      <c r="P12" t="n">
-        <v>35350</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17170</v>
-      </c>
-      <c r="R12" t="n">
-        <v>146000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>24000</v>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선, 방산, 원전 섹터 전반의 약세. 실적 부진 및 시장 기대치 하회.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선', '방산', '실적']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64100</v>
+        <v>64000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.07%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="H13" t="n">
         <v>22.23</v>
@@ -1622,7 +1622,7 @@
         <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>57359426050</v>
+        <v>58007377450</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전, 전력 섹터 전반의 소외감. 공매도 이슈 및 시장 변동성 확대.</t>
+          <t>원전 및 SMR 관련 뉴스에도 불구하고 주가 부진. 외인 매도 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '소외주']</t>
+          <t>['원전', 'SMR', '외인매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,70 +1667,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1605</v>
+        <v>3090</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.93</v>
+        <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="H14" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1573</v>
+        <v>3235</v>
       </c>
       <c r="K14" t="n">
-        <v>1650</v>
+        <v>3170</v>
       </c>
       <c r="L14" t="n">
-        <v>1715</v>
+        <v>3200</v>
       </c>
       <c r="M14" t="n">
-        <v>1573</v>
+        <v>3035</v>
       </c>
       <c r="N14" t="n">
-        <v>1.77</v>
+        <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>27509200808</v>
+        <v>9432994350</v>
       </c>
       <c r="P14" t="n">
-        <v>2970</v>
+        <v>7050</v>
       </c>
       <c r="Q14" t="n">
-        <v>890</v>
+        <v>2500</v>
       </c>
       <c r="R14" t="n">
-        <v>-746000</v>
+        <v>-32000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4270</v>
+        <v>4265</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>18923407175</v>
+        <v>19203897664</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-14.28%</t>
+          <t>'-14.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>18927122773</v>
+        <v>21408005755</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>

--- a/data/trending_integrated_20261021_12.xlsx
+++ b/data/trending_integrated_20261021_12.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10572345257</v>
+        <v>10573020257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14950</v>
+        <v>14985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.76%</t>
+          <t>'+24.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>88674869715</v>
+        <v>89363027370</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11170</v>
+        <v>11090</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.33%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>236224623010</v>
+        <v>239841973560</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 증가 및 신고가 경신. 로봇 섹터 강세.</t>
+          <t>인공지능 데이터센터 수주잔고 1조원 돌파라는 강력한 팩트에 기반한 신고가 경신 기대감이 높으며, 로봇주 섹터 내 대장주로서의 역할을 기대하고 있습니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주잔고', '신고가', '로봇']</t>
+          <t>['수주잔고', '인공지능', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9390</v>
+        <v>9420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.55%</t>
+          <t>'+8.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H5" t="n">
         <v>5.34</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>26018043855</v>
+        <v>26769596020</v>
       </c>
       <c r="P5" t="n">
         <v>14940</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회 이슈 속 거래량 증가 및 상승 기대감. 영업이익 호조.</t>
+          <t>자회사 나스닥 상장 철회 및 중복상장 금지 이슈 속에서 테슬라 관련 긍정적 뉴스와 함께 주가 상승에 대한 기대감이 나타나고 있습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['나스닥', '영업이익', '거래량']</t>
+          <t>['나스닥', '중복상장', '테슬라']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224000</v>
+        <v>225000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.91%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="G6" t="n">
-        <v>1866</v>
+        <v>1886</v>
       </c>
       <c r="H6" t="n">
         <v>46.08</v>
@@ -978,7 +978,7 @@
         <v>46.04</v>
       </c>
       <c r="O6" t="n">
-        <v>2112579952000</v>
+        <v>2155092470500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 동반 매수세 유입 및 미국발 반도체 관련 뉴스에 따른 상승 기대감. 25만원 돌파 여부가 관건.</t>
+          <t>외인 동반 매수세 유입과 미국 중국산 반도체 퇴출 결정 속보에 따른 상승 기대감이 형성되고 있습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '외인매수', '실적']</t>
+          <t>['외인유입', '반도체', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1292000</v>
+        <v>1293000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.64%</t>
+          <t>'+5.72%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G7" t="n">
-        <v>1755</v>
+        <v>1838</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>3066870962500</v>
+        <v>3104168664500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 및 마이크론 파업 예고 등의 뉴스 반영. 외인/기관 순매수세 유입.</t>
+          <t>자사주 매입 완료 및 외인, 기관 동반 매수세 유입에 대한 기대감이 있으나, 솔리다임 상장 관련 불확실성과 주가 하락 우려도 공존합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주', '외인매수', '마이크론']</t>
+          <t>['자사주매입', '외인기관', '솔리다임']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14790</v>
+        <v>14780</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.45%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="H8" t="n">
         <v>9.82</v>
@@ -1162,7 +1162,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>22592573380</v>
+        <v>22984284985</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 기반 상승 기대감 있으나, 주가 조작 및 정치적 이슈 언급하며 부정적 논조.</t>
+          <t>외국인 및 연기금의 꾸준한 매수세와 실적 기반 목표가 상향 가능성이 제기되고 있으나, 주가조작 의혹 및 상승폭에 대한 아쉬움이 나타납니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주가조작', '공매도']</t>
+          <t>['외국인', '연기금', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2935</v>
+        <v>2930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.35%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
         <v>5.82</v>
@@ -1254,7 +1254,7 @@
         <v>5.91</v>
       </c>
       <c r="O9" t="n">
-        <v>16117797689</v>
+        <v>16218121634</v>
       </c>
       <c r="P9" t="n">
         <v>19950</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7440</v>
+        <v>64200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.34%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>252</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K10" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L10" t="n">
-        <v>7520</v>
+        <v>64800</v>
       </c>
       <c r="M10" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N10" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O10" t="n">
-        <v>9494980700</v>
+        <v>58726482150</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>131000</v>
+        <v>-40000</v>
       </c>
       <c r="S10" t="n">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
+          <t>원전 및 전력 섹터 전반의 소외 현상과 외인 매도세, 정부의 무능력에 대한 비판 속에서 주가 부양에 대한 기대보다는 하락 우려가 더 큰 상황입니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
+          <t>['원전', '외인매도', '소외']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17670</v>
+        <v>7430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="H11" t="n">
-        <v>27.78</v>
+        <v>25.45</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17320</v>
+        <v>7270</v>
       </c>
       <c r="K11" t="n">
-        <v>17480</v>
+        <v>7360</v>
       </c>
       <c r="L11" t="n">
-        <v>17820</v>
+        <v>7520</v>
       </c>
       <c r="M11" t="n">
-        <v>17170</v>
+        <v>7250</v>
       </c>
       <c r="N11" t="n">
-        <v>27.78</v>
+        <v>25.4</v>
       </c>
       <c r="O11" t="n">
-        <v>27643319170</v>
+        <v>9709962090</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>17170</v>
+        <v>7190</v>
       </c>
       <c r="R11" t="n">
-        <v>146000</v>
+        <v>131000</v>
       </c>
       <c r="S11" t="n">
-        <v>24000</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선, 방산, 원전 섹터 전반의 약세. 실적 부진 및 시장 기대치 하회.</t>
+          <t>개인 투자자들의 피로감과 회사의 저평가 및 상폐 가능성 언급. 외국인 비중 변화 및 주가 흐름에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선', '방산', '실적']</t>
+          <t>['개인 투자자', '상폐 가능성', '저평가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1604</v>
+        <v>17670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
-        <v>0.84</v>
+        <v>27.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1573</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>1650</v>
+        <v>17480</v>
       </c>
       <c r="L12" t="n">
-        <v>1715</v>
+        <v>17820</v>
       </c>
       <c r="M12" t="n">
-        <v>1573</v>
+        <v>17170</v>
       </c>
       <c r="N12" t="n">
-        <v>1.77</v>
+        <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>27605260594</v>
+        <v>28417392500</v>
       </c>
       <c r="P12" t="n">
-        <v>2970</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>890</v>
+        <v>17170</v>
       </c>
       <c r="R12" t="n">
-        <v>-746000</v>
+        <v>146000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>정치적 이슈와 맞물려 주가 하락에 대한 우려가 크며, 실적 부진 및 향후 주가 전망에 대한 부정적인 의견이 지배적입니다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,51 +1555,51 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['정치적', '실적', '하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64000</v>
+        <v>1604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.93</v>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>423</v>
+        <v>207</v>
       </c>
       <c r="H13" t="n">
-        <v>22.23</v>
+        <v>0.84</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62800</v>
+        <v>1573</v>
       </c>
       <c r="K13" t="n">
-        <v>63600</v>
+        <v>1650</v>
       </c>
       <c r="L13" t="n">
-        <v>64800</v>
+        <v>1715</v>
       </c>
       <c r="M13" t="n">
-        <v>62600</v>
+        <v>1573</v>
       </c>
       <c r="N13" t="n">
-        <v>22.29</v>
+        <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>58007377450</v>
+        <v>27757476241</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>2970</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>890</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>-746000</v>
       </c>
       <c r="S13" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전 및 SMR 관련 뉴스에도 불구하고 주가 부진. 외인 매도 및 정부 정책 비판.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '외인매도']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3090</v>
+        <v>3095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.73</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0.73</v>
       </c>
       <c r="O14" t="n">
-        <v>9432994350</v>
+        <v>9575440615</v>
       </c>
       <c r="P14" t="n">
         <v>7050</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4265</v>
+        <v>4280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-7.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="H15" t="n">
         <v>8.58</v>
@@ -1806,7 +1806,7 @@
         <v>8.57</v>
       </c>
       <c r="O15" t="n">
-        <v>19203897664</v>
+        <v>19650483479</v>
       </c>
       <c r="P15" t="n">
         <v>7560</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>프로그램 매도 및 공매도 집중으로 인한 주가 하락. 경영진 비판.</t>
+          <t>프로그램 매도세와 공매도 심화 속 주가 하락 우려가 제기되고 있으며, 배당 및 경영진에 대한 불만이 표출되고 있습니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매도', '주가 하락']</t>
+          <t>['공매도', '프로그램매도', '주가하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-14.80%</t>
+          <t>'-15.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H16" t="n">
         <v>0.6899999999999999</v>
@@ -1898,7 +1898,7 @@
         <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>21408005755</v>
+        <v>22017140775</v>
       </c>
       <c r="P16" t="n">
         <v>3980</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>하한가 기록 후 추가 하락 우려. 자본 잠식 및 부도설 제기.</t>
+          <t>현저한 시황변동 조회공시 요구 및 자본잠식, 횡령, 부도 가능성에 대한 우려로 주가 급락 및 거래정지, 상폐에 대한 공포감이 형성되고 있습니다.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['하한가', '자본 잠식', '부도']</t>
+          <t>['조회공시', '자본잠식', '거래정지']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">

--- a/data/trending_integrated_20261021_12.xlsx
+++ b/data/trending_integrated_20261021_12.xlsx
@@ -578,13 +578,13 @@
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10573020257</v>
+        <v>10575435257</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14985</v>
+        <v>1882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.05%</t>
+          <t>'+23.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12080</v>
+        <v>1520</v>
       </c>
       <c r="K3" t="n">
-        <v>12280</v>
+        <v>1132</v>
       </c>
       <c r="L3" t="n">
-        <v>15640</v>
+        <v>1952</v>
       </c>
       <c r="M3" t="n">
-        <v>12280</v>
+        <v>1115</v>
       </c>
       <c r="N3" t="n">
-        <v>0.27</v>
+        <v>0.57</v>
       </c>
       <c r="O3" t="n">
-        <v>89363027370</v>
+        <v>47737512063</v>
       </c>
       <c r="P3" t="n">
-        <v>28800</v>
+        <v>3980</v>
       </c>
       <c r="Q3" t="n">
-        <v>12030</v>
+        <v>1115</v>
       </c>
       <c r="R3" t="n">
-        <v>139000</v>
+        <v>393000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
+          <t>경영권 인수 관련 구체적인 공시가 확인되었으며, 이를 바탕으로 상한가 기대감이 높아지며 급등세를 보임.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['노광 장비', '엘리스', '급등']</t>
+          <t>['경영권인수', '공시', '3연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11090</v>
+        <v>14890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.51%</t>
+          <t>'+23.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>408</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,143 +779,143 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9770</v>
+        <v>12080</v>
       </c>
       <c r="K4" t="n">
-        <v>10320</v>
+        <v>12280</v>
       </c>
       <c r="L4" t="n">
-        <v>11690</v>
+        <v>15640</v>
       </c>
       <c r="M4" t="n">
-        <v>9690</v>
+        <v>12280</v>
       </c>
       <c r="N4" t="n">
-        <v>0.88</v>
+        <v>0.27</v>
       </c>
       <c r="O4" t="n">
-        <v>239841973560</v>
+        <v>91395230890</v>
       </c>
       <c r="P4" t="n">
-        <v>11690</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>12030</v>
       </c>
       <c r="R4" t="n">
-        <v>350000</v>
+        <v>139000</v>
       </c>
       <c r="S4" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주잔고 1조원 돌파라는 강력한 팩트에 기반한 신고가 경신 기대감이 높으며, 로봇주 섹터 내 대장주로서의 역할을 기대하고 있습니다.</t>
+          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수주잔고', '인공지능', '신고가']</t>
+          <t>['노광 장비', '엘리스', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9420</v>
+        <v>11235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.90%</t>
+          <t>'+14.99%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.66</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>258</v>
+        <v>423</v>
       </c>
       <c r="H5" t="n">
-        <v>5.34</v>
+        <v>1.28</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8650</v>
+        <v>9770</v>
       </c>
       <c r="K5" t="n">
-        <v>9010</v>
+        <v>10320</v>
       </c>
       <c r="L5" t="n">
-        <v>9610</v>
+        <v>11690</v>
       </c>
       <c r="M5" t="n">
-        <v>8790</v>
+        <v>9690</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>26769596020</v>
+        <v>257941590775</v>
       </c>
       <c r="P5" t="n">
-        <v>14940</v>
+        <v>11690</v>
       </c>
       <c r="Q5" t="n">
-        <v>5390</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>225000</v>
+        <v>350000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 나스닥 상장 철회 및 중복상장 금지 이슈 속에서 테슬라 관련 긍정적 뉴스와 함께 주가 상승에 대한 기대감이 나타나고 있습니다.</t>
+          <t>데이터센터 수주 잔고 증가 및 로봇 관련 긍정적 전망에 힘입어 신고가 경신 가능성이 제기되며 강한 상승세를 보임.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['나스닥', '중복상장', '테슬라']</t>
+          <t>['수주잔고', '로봇주', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>9320</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+7.75%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G6" t="n">
+        <v>283</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>8650</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9010</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9610</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8790</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27944186075</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14940</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5390</v>
+      </c>
+      <c r="R6" t="n">
         <v>225000</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>'+6.38%</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E6" t="n">
-        <v>800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>502</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1886</v>
-      </c>
-      <c r="H6" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>211500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>217000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>228000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>217000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2155092470500</v>
-      </c>
-      <c r="P6" t="n">
-        <v>374500</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>94500</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1981000</v>
-      </c>
       <c r="S6" t="n">
-        <v>380000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외인 동반 매수세 유입과 미국 중국산 반도체 퇴출 결정 속보에 따른 상승 기대감이 형성되고 있습니다.</t>
+          <t>테슬라 관련 긍정적 뉴스 및 실적 전망에 힘입어 거래량이 증가하며 주가 상승에 대한 기대감이 반영됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인유입', '반도체', '상승']</t>
+          <t>['테슬라', '영업이익', '주가상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1293000</v>
+        <v>223000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.72%</t>
+          <t>'+5.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="G7" t="n">
-        <v>1838</v>
+        <v>1922</v>
       </c>
       <c r="H7" t="n">
-        <v>48.77</v>
+        <v>46.08</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1223000</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>1260000</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>1329000</v>
+        <v>228000</v>
       </c>
       <c r="M7" t="n">
-        <v>1258000</v>
+        <v>217000</v>
       </c>
       <c r="N7" t="n">
-        <v>48.81</v>
+        <v>46.04</v>
       </c>
       <c r="O7" t="n">
-        <v>3104168664500</v>
+        <v>2304318212750</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>468000</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>150000</v>
+        <v>1981000</v>
       </c>
       <c r="S7" t="n">
-        <v>73000</v>
+        <v>380000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 및 외인, 기관 동반 매수세 유입에 대한 기대감이 있으나, 솔리다임 상장 관련 불확실성과 주가 하락 우려도 공존합니다.</t>
+          <t>미국발 반도체 규제 이슈와 함께 외인 순매수 유입이 확인되었으나, 개인 투자자들의 관망세 속에서 주가 상승 탄력이 제한적인 모습.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주매입', '외인기관', '솔리다임']</t>
+          <t>['반도체', '외인유입', '하방다지기']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14780</v>
+        <v>1283000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>485</v>
       </c>
       <c r="G8" t="n">
-        <v>199</v>
+        <v>1795</v>
       </c>
       <c r="H8" t="n">
-        <v>9.82</v>
+        <v>48.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14160</v>
+        <v>1223000</v>
       </c>
       <c r="K8" t="n">
-        <v>14340</v>
+        <v>1260000</v>
       </c>
       <c r="L8" t="n">
-        <v>14820</v>
+        <v>1329000</v>
       </c>
       <c r="M8" t="n">
-        <v>14340</v>
+        <v>1258000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.779999999999999</v>
+        <v>48.81</v>
       </c>
       <c r="O8" t="n">
-        <v>22984284985</v>
+        <v>3276529464000</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>468000</v>
       </c>
       <c r="R8" t="n">
-        <v>133000</v>
+        <v>150000</v>
       </c>
       <c r="S8" t="n">
-        <v>9000</v>
+        <v>73000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외국인 및 연기금의 꾸준한 매수세와 실적 기반 목표가 상향 가능성이 제기되고 있으나, 주가조작 의혹 및 상승폭에 대한 아쉬움이 나타납니다.</t>
+          <t>자사주 매입 완료 및 솔리다임 관련 뉴스가 주가 반등 기대감을 높였으나, 기관 매도세가 관찰되며 변동성을 보임.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외국인', '연기금', '실적']</t>
+          <t>['자사주매입', '솔리다임', '반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,178 +1200,178 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2930</v>
+        <v>14810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+4.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H9" t="n">
-        <v>5.82</v>
+        <v>9.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2840</v>
+        <v>14160</v>
       </c>
       <c r="K9" t="n">
-        <v>3100</v>
+        <v>14340</v>
       </c>
       <c r="L9" t="n">
-        <v>3300</v>
+        <v>14820</v>
       </c>
       <c r="M9" t="n">
-        <v>2855</v>
+        <v>14340</v>
       </c>
       <c r="N9" t="n">
-        <v>5.91</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>16218121634</v>
+        <v>24432263405</v>
       </c>
       <c r="P9" t="n">
-        <v>19950</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1913</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-1166000</v>
+        <v>133000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
+          <t>외국인 및 연기금의 꾸준한 매수세가 관찰되며 실적 개선 기대감이 존재하나, 주가 상승폭은 제한적인 상황.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우주섹터', '주가조작', '투자기업']</t>
+          <t>['외국인매수', '연기금', '실적주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64200</v>
+        <v>2935</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.23%</t>
+          <t>'+3.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>443</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
-        <v>22.23</v>
+        <v>5.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>62800</v>
+        <v>2840</v>
       </c>
       <c r="K10" t="n">
-        <v>63600</v>
+        <v>3100</v>
       </c>
       <c r="L10" t="n">
-        <v>64800</v>
+        <v>3300</v>
       </c>
       <c r="M10" t="n">
-        <v>62600</v>
+        <v>2855</v>
       </c>
       <c r="N10" t="n">
-        <v>22.29</v>
+        <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>58726482150</v>
+        <v>16385456709</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>19950</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>1913</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>-1200000</v>
       </c>
       <c r="S10" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전 및 전력 섹터 전반의 소외 현상과 외인 매도세, 정부의 무능력에 대한 비판 속에서 주가 부양에 대한 기대보다는 하락 우려가 더 큰 상황입니다.</t>
+          <t>우주 섹터 관련 언급과 함께 주가 조작 의혹 제기. 반등 기대와 함께 신고 주장.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '외인매도', '소외']</t>
+          <t>['우주섹터', '주가조작', '투자기업']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7430</v>
+        <v>7440</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="H11" t="n">
         <v>25.45</v>
@@ -1438,7 +1438,7 @@
         <v>25.4</v>
       </c>
       <c r="O11" t="n">
-        <v>9709962090</v>
+        <v>10717334430</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17670</v>
+        <v>64200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>459</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>22.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>62800</v>
       </c>
       <c r="K12" t="n">
-        <v>17480</v>
+        <v>63600</v>
       </c>
       <c r="L12" t="n">
-        <v>17820</v>
+        <v>64800</v>
       </c>
       <c r="M12" t="n">
-        <v>17170</v>
+        <v>62600</v>
       </c>
       <c r="N12" t="n">
-        <v>27.78</v>
+        <v>22.29</v>
       </c>
       <c r="O12" t="n">
-        <v>28417392500</v>
+        <v>63514127800</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>17170</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>146000</v>
+        <v>-40000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 주가 하락에 대한 우려가 크며, 실적 부진 및 향후 주가 전망에 대한 부정적인 의견이 지배적입니다.</t>
+          <t>원전 및 전력 관련 섹터 전반의 부진한 흐름 속에서, 기관의 매도세와 정부 정책에 대한 불신이 주가 하락 요인으로 작용함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치적', '실적', '하락']</t>
+          <t>['원전주', '공매도', '정부정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1604</v>
+        <v>17700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H13" t="n">
-        <v>0.84</v>
+        <v>27.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1573</v>
+        <v>17320</v>
       </c>
       <c r="K13" t="n">
-        <v>1650</v>
+        <v>17480</v>
       </c>
       <c r="L13" t="n">
-        <v>1715</v>
+        <v>17820</v>
       </c>
       <c r="M13" t="n">
-        <v>1573</v>
+        <v>17170</v>
       </c>
       <c r="N13" t="n">
-        <v>1.77</v>
+        <v>27.78</v>
       </c>
       <c r="O13" t="n">
-        <v>27757476241</v>
+        <v>31059710505</v>
       </c>
       <c r="P13" t="n">
-        <v>2970</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>890</v>
+        <v>17170</v>
       </c>
       <c r="R13" t="n">
-        <v>-746000</v>
+        <v>146000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
+          <t>현 주가에 대한 부정적 전망과 함께 정치적 이슈가 언급되며 투자 심리가 위축됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,90 +1647,90 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['스페이스X', '수혜주', '거래량']</t>
+          <t>['최저가', '떡락', '정치이슈']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3095</v>
+        <v>1593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.33%</t>
+          <t>'+1.27%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.73</v>
+        <v>-0.93</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3235</v>
+        <v>1573</v>
       </c>
       <c r="K14" t="n">
-        <v>3170</v>
+        <v>1650</v>
       </c>
       <c r="L14" t="n">
-        <v>3200</v>
+        <v>1715</v>
       </c>
       <c r="M14" t="n">
-        <v>3035</v>
+        <v>1573</v>
       </c>
       <c r="N14" t="n">
-        <v>0.73</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>9575440615</v>
+        <v>28307061013</v>
       </c>
       <c r="P14" t="n">
-        <v>7050</v>
+        <v>2970</v>
       </c>
       <c r="Q14" t="n">
-        <v>2500</v>
+        <v>890</v>
       </c>
       <c r="R14" t="n">
-        <v>-32000</v>
+        <v>-746000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
+          <t>스페이스X 수혜 기대감 속 거래량 증가. 단기 급등 가능성 있으나 윗꼬리 부담.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
+          <t>['스페이스X', '수혜주', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,169 +1752,169 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4280</v>
+        <v>3110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.56%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>451</v>
+        <v>207</v>
       </c>
       <c r="H15" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4630</v>
+        <v>3235</v>
       </c>
       <c r="K15" t="n">
-        <v>4645</v>
+        <v>3170</v>
       </c>
       <c r="L15" t="n">
-        <v>4645</v>
+        <v>3200</v>
       </c>
       <c r="M15" t="n">
-        <v>4240</v>
+        <v>3035</v>
       </c>
       <c r="N15" t="n">
-        <v>8.57</v>
+        <v>0.73</v>
       </c>
       <c r="O15" t="n">
-        <v>19650483479</v>
+        <v>9969769438</v>
       </c>
       <c r="P15" t="n">
-        <v>7560</v>
+        <v>7050</v>
       </c>
       <c r="Q15" t="n">
-        <v>2930</v>
+        <v>2500</v>
       </c>
       <c r="R15" t="n">
-        <v>-1027000</v>
+        <v>-103000</v>
       </c>
       <c r="S15" t="n">
-        <v>-162000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>프로그램 매도세와 공매도 심화 속 주가 하락 우려가 제기되고 있으며, 배당 및 경영진에 대한 불만이 표출되고 있습니다.</t>
+          <t>김정은 사망설 관련 북한발 뉴스로 인한 급락 및 투자자 불안 심리 고조. 공매도 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매도', '주가하락']</t>
+          <t>['김정은 사망설', '북한 뉴스', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1289</v>
+        <v>4292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-15.20%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>109</v>
+        <v>491</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1520</v>
+        <v>4630</v>
       </c>
       <c r="K16" t="n">
-        <v>1132</v>
+        <v>4645</v>
       </c>
       <c r="L16" t="n">
-        <v>1480</v>
+        <v>4645</v>
       </c>
       <c r="M16" t="n">
-        <v>1115</v>
+        <v>4240</v>
       </c>
       <c r="N16" t="n">
-        <v>0.57</v>
+        <v>8.57</v>
       </c>
       <c r="O16" t="n">
-        <v>22017140775</v>
+        <v>20570873651</v>
       </c>
       <c r="P16" t="n">
-        <v>3980</v>
+        <v>7560</v>
       </c>
       <c r="Q16" t="n">
-        <v>1115</v>
+        <v>2930</v>
       </c>
       <c r="R16" t="n">
-        <v>393000</v>
+        <v>-1027000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-162000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>현저한 시황변동 조회공시 요구 및 자본잠식, 횡령, 부도 가능성에 대한 우려로 주가 급락 및 거래정지, 상폐에 대한 공포감이 형성되고 있습니다.</t>
+          <t>주가 하락 압력이 지속되는 가운데, 프로그램 매도 물량이 거래량의 상당 부분을 차지하며 부정적인 시장 심리가 고조됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['조회공시', '자본잠식', '거래정지']</t>
+          <t>['주가누르기', '공매도', '프로그램매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>088350</t>
         </is>
       </c>
     </row>
